--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>3150</x:v>
+        <x:v>3270</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>149760</x:v>
+        <x:v>155760</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>3270</x:v>
+        <x:v>3540</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>155760</x:v>
+        <x:v>169260</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>3540</x:v>
+        <x:v>3630</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1151,7 +1151,7 @@
       </x:c>
       <x:c r="C20" s="12" t="s"/>
       <x:c r="D20" s="17" t="n">
-        <x:v>18600</x:v>
+        <x:v>20850</x:v>
       </x:c>
       <x:c r="E20" s="8" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>169260</x:v>
+        <x:v>173760</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>3630</x:v>
+        <x:v>5010</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1151,7 +1151,7 @@
       </x:c>
       <x:c r="C20" s="12" t="s"/>
       <x:c r="D20" s="17" t="n">
-        <x:v>20850</x:v>
+        <x:v>22200</x:v>
       </x:c>
       <x:c r="E20" s="8" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>173760</x:v>
+        <x:v>227580</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>5010</x:v>
+        <x:v>5040</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>227580</x:v>
+        <x:v>229080</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>5040</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>229080</x:v>
+        <x:v>229800</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>5070</x:v>
+        <x:v>5160</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>229800</x:v>
+        <x:v>234300</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>5160</x:v>
+        <x:v>3840</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1151,7 +1151,7 @@
       </x:c>
       <x:c r="C20" s="12" t="s"/>
       <x:c r="D20" s="17" t="n">
-        <x:v>22200</x:v>
+        <x:v>20850</x:v>
       </x:c>
       <x:c r="E20" s="8" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>234300</x:v>
+        <x:v>181980</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>3840</x:v>
+        <x:v>3870</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>181980</x:v>
+        <x:v>186480</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>3870</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>186480</x:v>
+        <x:v>184980</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>3900</x:v>
+        <x:v>3960</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>184980</x:v>
+        <x:v>187980</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>3960</x:v>
+        <x:v>3990</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>3990</x:v>
+        <x:v>4020</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>187980</x:v>
+        <x:v>189480</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>4020</x:v>
+        <x:v>4050</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1151,7 +1151,7 @@
       </x:c>
       <x:c r="C20" s="12" t="s"/>
       <x:c r="D20" s="17" t="n">
-        <x:v>20850</x:v>
+        <x:v>21450</x:v>
       </x:c>
       <x:c r="E20" s="8" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>189480</x:v>
+        <x:v>190200</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>4050</x:v>
+        <x:v>4110</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1072,7 +1072,7 @@
       </x:c>
       <x:c r="C17" s="12" t="s"/>
       <x:c r="D17" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E17" s="8" t="s"/>
       <x:c r="F17" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>4110</x:v>
+        <x:v>4200</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>190200</x:v>
+        <x:v>191700</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>4200</x:v>
+        <x:v>4350</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1072,7 +1072,7 @@
       </x:c>
       <x:c r="C17" s="12" t="s"/>
       <x:c r="D17" s="18" t="n">
-        <x:v>180</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E17" s="8" t="s"/>
       <x:c r="F17" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>191700</x:v>
+        <x:v>197700</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>4350</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>197700</x:v>
+        <x:v>203700</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>4500</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>203700</x:v>
+        <x:v>205200</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>4530</x:v>
+        <x:v>4560</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -834,7 +834,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D26" s="1" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s"/>
       <x:c r="F26" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>5460</x:v>
+        <x:v>5520</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>28650</x:v>
+        <x:v>29250</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>233580</x:v>
+        <x:v>234300</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>29250</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>234300</x:v>
+        <x:v>235020</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>5520</x:v>
+        <x:v>5580</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>235020</x:v>
+        <x:v>238020</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>5580</x:v>
+        <x:v>5670</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>30000</x:v>
+        <x:v>33000</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>238020</x:v>
+        <x:v>242520</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>5670</x:v>
+        <x:v>5700</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>242520</x:v>
+        <x:v>244020</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>5700</x:v>
+        <x:v>5880</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>33000</x:v>
+        <x:v>33750</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>244020</x:v>
+        <x:v>250020</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>5880</x:v>
+        <x:v>5910</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>250020</x:v>
+        <x:v>251520</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>5910</x:v>
+        <x:v>5940</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>33750</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>251520</x:v>
+        <x:v>253020</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>5940</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>35000</x:v>
+        <x:v>35700</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>253020</x:v>
+        <x:v>254460</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6000</x:v>
+        <x:v>6090</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>35700</x:v>
+        <x:v>39450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>254460</x:v>
+        <x:v>258960</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6090</x:v>
+        <x:v>6120</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>258960</x:v>
+        <x:v>260460</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>39450</x:v>
+        <x:v>37950</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6120</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6150</x:v>
+        <x:v>6180</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>260460</x:v>
+        <x:v>261960</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6180</x:v>
+        <x:v>6300</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>261960</x:v>
+        <x:v>267960</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6300</x:v>
+        <x:v>6420</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>267960</x:v>
+        <x:v>270960</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6420</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>270960</x:v>
+        <x:v>272460</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6450</x:v>
+        <x:v>6510</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>37950</x:v>
+        <x:v>39450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>272460</x:v>
+        <x:v>275460</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6510</x:v>
+        <x:v>6540</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6540</x:v>
+        <x:v>6570</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6570</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>275460</x:v>
+        <x:v>276960</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6600</x:v>
+        <x:v>6630</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>276960</x:v>
+        <x:v>278460</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6630</x:v>
+        <x:v>6780</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>39450</x:v>
+        <x:v>42450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>278460</x:v>
+        <x:v>288960</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6780</x:v>
+        <x:v>6840</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>288960</x:v>
+        <x:v>291960</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -27,7 +27,7 @@
     <x:t>AND INCOME DEPOSITED WITH THE BUREAU OF TREASURY</x:t>
   </x:si>
   <x:si>
-    <x:t>FOR THE MONTH OF April 2026</x:t>
+    <x:t>FOR THE MONTH OF May 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Department of Information and Communications Technology</x:t>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6840</x:v>
+        <x:v>6900</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6900</x:v>
+        <x:v>6960</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>6960</x:v>
+        <x:v>7020</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>291960</x:v>
+        <x:v>294960</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7020</x:v>
+        <x:v>7110</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>294960</x:v>
+        <x:v>298680</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7110</x:v>
+        <x:v>7140</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>298680</x:v>
+        <x:v>300180</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7140</x:v>
+        <x:v>7230</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>300180</x:v>
+        <x:v>303900</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7230</x:v>
+        <x:v>7260</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>303900</x:v>
+        <x:v>305400</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7260</x:v>
+        <x:v>7320</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>42450</x:v>
+        <x:v>43200</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>305400</x:v>
+        <x:v>308400</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7320</x:v>
+        <x:v>7350</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>308400</x:v>
+        <x:v>309900</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7350</x:v>
+        <x:v>7410</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>43200</x:v>
+        <x:v>43950</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>309900</x:v>
+        <x:v>312900</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7410</x:v>
+        <x:v>7440</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>312900</x:v>
+        <x:v>314400</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7440</x:v>
+        <x:v>7470</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>314400</x:v>
+        <x:v>315900</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7470</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>43950</x:v>
+        <x:v>46450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>315900</x:v>
+        <x:v>316620</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7500</x:v>
+        <x:v>7590</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>46450</x:v>
+        <x:v>48700</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>316620</x:v>
+        <x:v>321120</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7590</x:v>
+        <x:v>7830</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>48700</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>321120</x:v>
+        <x:v>333120</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7830</x:v>
+        <x:v>7860</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>333120</x:v>
+        <x:v>334620</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7860</x:v>
+        <x:v>7950</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>334620</x:v>
+        <x:v>339120</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>7950</x:v>
+        <x:v>8610</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>51700</x:v>
+        <x:v>52450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>339120</x:v>
+        <x:v>371340</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>8610</x:v>
+        <x:v>9180</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>52450</x:v>
+        <x:v>64450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>371340</x:v>
+        <x:v>400500</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>
@@ -834,7 +834,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D26" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s"/>
       <x:c r="F26" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>9180</x:v>
+        <x:v>9240</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>64450</x:v>
+        <x:v>70450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>400500</x:v>
+        <x:v>409500</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>9240</x:v>
+        <x:v>9570</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>70450</x:v>
+        <x:v>71650</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>409500</x:v>
+        <x:v>421980</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>9570</x:v>
+        <x:v>9630</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>71650</x:v>
+        <x:v>73150</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>421980</x:v>
+        <x:v>424980</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>9630</x:v>
+        <x:v>9690</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>424980</x:v>
+        <x:v>427980</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>9690</x:v>
+        <x:v>9750</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>427980</x:v>
+        <x:v>434640</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>9750</x:v>
+        <x:v>9810</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>73150</x:v>
+        <x:v>73900</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>434640</x:v>
+        <x:v>437640</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>9810</x:v>
+        <x:v>9870</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>437640</x:v>
+        <x:v>439080</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>9870</x:v>
+        <x:v>9930</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>73900</x:v>
+        <x:v>75700</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>439080</x:v>
+        <x:v>441300</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>9930</x:v>
+        <x:v>9960</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>441300</x:v>
+        <x:v>442800</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>9960</x:v>
+        <x:v>9990</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>442800</x:v>
+        <x:v>444300</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>9990</x:v>
+        <x:v>10110</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>444300</x:v>
+        <x:v>450300</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>10110</x:v>
+        <x:v>10140</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>75700</x:v>
+        <x:v>76450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>450300</x:v>
+        <x:v>451800</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>10140</x:v>
+        <x:v>10200</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>451800</x:v>
+        <x:v>454800</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>10200</x:v>
+        <x:v>10230</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>454800</x:v>
+        <x:v>456300</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>10230</x:v>
+        <x:v>10320</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>76450</x:v>
+        <x:v>77950</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>456300</x:v>
+        <x:v>462300</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>10320</x:v>
+        <x:v>10620</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>462300</x:v>
+        <x:v>477300</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>10620</x:v>
+        <x:v>10680</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>77950</x:v>
+        <x:v>78700</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>477300</x:v>
+        <x:v>480300</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -27,7 +27,7 @@
     <x:t>AND INCOME DEPOSITED WITH THE BUREAU OF TREASURY</x:t>
   </x:si>
   <x:si>
-    <x:t>FOR THE MONTH OF May 2026</x:t>
+    <x:t>FOR THE MONTH OF June 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Department of Information and Communications Technology</x:t>
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>10680</x:v>
+        <x:v>10740</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>480300</x:v>
+        <x:v>483300</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>10740</x:v>
+        <x:v>10860</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>78700</x:v>
+        <x:v>79450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>483300</x:v>
+        <x:v>489300</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>10860</x:v>
+        <x:v>10890</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>489300</x:v>
+        <x:v>490800</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>10890</x:v>
+        <x:v>10920</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>490800</x:v>
+        <x:v>492300</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>10920</x:v>
+        <x:v>11070</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>79450</x:v>
+        <x:v>81250</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>492300</x:v>
+        <x:v>499740</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>11070</x:v>
+        <x:v>11100</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>499740</x:v>
+        <x:v>500460</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>500460</x:v>
+        <x:v>501180</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>11100</x:v>
+        <x:v>11130</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>11130</x:v>
+        <x:v>11100</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>81250</x:v>
+        <x:v>77850</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>501180</x:v>
+        <x:v>504180</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>77850</x:v>
+        <x:v>79350</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>504180</x:v>
+        <x:v>510180</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>510180</x:v>
+        <x:v>514680</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>11100</x:v>
+        <x:v>11340</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>79350</x:v>
+        <x:v>80600</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>514680</x:v>
+        <x:v>523680</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>11340</x:v>
+        <x:v>11550</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>523680</x:v>
+        <x:v>541680</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>11550</x:v>
+        <x:v>11580</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>541680</x:v>
+        <x:v>543180</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>80600</x:v>
+        <x:v>80100</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>543180</x:v>
+        <x:v>535680</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>80100</x:v>
+        <x:v>80850</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>11580</x:v>
+        <x:v>11550</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>11550</x:v>
+        <x:v>11940</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>535680</x:v>
+        <x:v>555180</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>11940</x:v>
+        <x:v>11970</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>555180</x:v>
+        <x:v>556680</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>11970</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>80850</x:v>
+        <x:v>81450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>556680</x:v>
+        <x:v>557400</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12000</x:v>
+        <x:v>12030</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>81450</x:v>
+        <x:v>82200</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>557400</x:v>
+        <x:v>558900</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12030</x:v>
+        <x:v>12060</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>558900</x:v>
+        <x:v>561060</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12060</x:v>
+        <x:v>12090</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>561060</x:v>
+        <x:v>561780</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12090</x:v>
+        <x:v>12240</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>82200</x:v>
+        <x:v>82950</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>561780</x:v>
+        <x:v>569280</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12240</x:v>
+        <x:v>12330</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>82950</x:v>
+        <x:v>83700</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>569280</x:v>
+        <x:v>573780</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12330</x:v>
+        <x:v>12390</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>573780</x:v>
+        <x:v>575280</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12390</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>575280</x:v>
+        <x:v>578280</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12450</x:v>
+        <x:v>12480</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>578280</x:v>
+        <x:v>579780</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12480</x:v>
+        <x:v>12540</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>83700</x:v>
+        <x:v>84450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>579780</x:v>
+        <x:v>582780</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12540</x:v>
+        <x:v>12570</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>582780</x:v>
+        <x:v>584280</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12570</x:v>
+        <x:v>12600</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>584280</x:v>
+        <x:v>585780</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12600</x:v>
+        <x:v>12660</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>585780</x:v>
+        <x:v>588780</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12660</x:v>
+        <x:v>12720</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>588780</x:v>
+        <x:v>591780</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12720</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>591780</x:v>
+        <x:v>593280</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>12750</x:v>
+        <x:v>13020</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>593280</x:v>
+        <x:v>606780</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>13020</x:v>
+        <x:v>13170</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>606780</x:v>
+        <x:v>614280</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>13170</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>614280</x:v>
+        <x:v>615780</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>13200</x:v>
+        <x:v>13260</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>84450</x:v>
+        <x:v>87450</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>615780</x:v>
+        <x:v>618780</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>13260</x:v>
+        <x:v>13290</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>618780</x:v>
+        <x:v>620280</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>620280</x:v>
+        <x:v>623280</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -27,7 +27,7 @@
     <x:t>AND INCOME DEPOSITED WITH THE BUREAU OF TREASURY</x:t>
   </x:si>
   <x:si>
-    <x:t>FOR THE MONTH OF June 2026</x:t>
+    <x:t>FOR THE MONTH OF July 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Department of Information and Communications Technology</x:t>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>13290</x:v>
+        <x:v>13320</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>87450</x:v>
+        <x:v>89250</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>623280</x:v>
+        <x:v>624000</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>13320</x:v>
+        <x:v>13410</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>89250</x:v>
+        <x:v>90750</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>624000</x:v>
+        <x:v>628440</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:IV-A.xlsx
+++ b/reports/excel-reports_cache_report:IV-A.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>13410</x:v>
+        <x:v>13620</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>90750</x:v>
+        <x:v>92250</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>628440</x:v>
+        <x:v>638940</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>
